--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78772CA-FB28-4676-B532-3AF362ACBF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EECF61-47CA-44F7-9652-A023B1B1D46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="72600" yWindow="2805" windowWidth="21600" windowHeight="11175" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="fw release" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>루멘스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,6 +72,61 @@
   </si>
   <si>
     <t>사무실 보유 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김용근 소장님</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Number</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Release 날짜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"25. 11. 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Initial Release</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"25. 11. 21</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low Current Mode, Multi-Byte 기능 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_251110.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_251121.hex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_251121_30mA.hex</t>
+  </si>
+  <si>
+    <t>2-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -132,7 +188,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -144,6 +200,12 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,15 +541,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D710C5DD-EB3F-405B-9177-DB5793DB6340}">
-  <dimension ref="B2:H17"/>
+  <dimension ref="B2:I18"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
@@ -500,11 +563,16 @@
       <c r="E2" s="3">
         <v>45972</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="3">
+        <v>45981</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -517,96 +585,198 @@
       <c r="E3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="I3">
+        <f>SUM(C3:H3)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I7" si="0">SUM(C4:H4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7">
         <v>4</v>
       </c>
-      <c r="C7" s="1">
-        <f>SUM(C3:I5)</f>
+      <c r="I7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
+        <f>SUM(I3:I7)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>45971</v>
+      </c>
+      <c r="E11" s="3">
+        <v>45972</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B14" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B15" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="1">
+        <f>SUM(C12:I14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <f>35-(C8-C16)</f>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
+  <dimension ref="B2:E5"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.58203125" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B3" s="4">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="3">
-        <v>45971</v>
-      </c>
-      <c r="E10" s="3">
-        <v>45972</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="1">
-        <f>SUM(C11:I13)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17">
-        <f>35-(C7-C15)</f>
-        <v>19</v>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EECF61-47CA-44F7-9652-A023B1B1D46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47746CAB-B49B-432A-97F1-B93BE964E326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>루멘스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -127,6 +127,10 @@
   </si>
   <si>
     <t>이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고장</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -541,13 +545,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D710C5DD-EB3F-405B-9177-DB5793DB6340}">
-  <dimension ref="B2:I18"/>
+  <dimension ref="B2:I19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.45">
@@ -566,8 +570,12 @@
       <c r="F2" s="3">
         <v>45981</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="G2" s="3">
+        <v>45985</v>
+      </c>
+      <c r="H2" s="3">
+        <v>45986</v>
+      </c>
       <c r="I2" s="2" t="s">
         <v>10</v>
       </c>
@@ -585,9 +593,12 @@
       <c r="E3">
         <v>1</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
       <c r="I3">
         <f>SUM(C3:H3)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.45">
@@ -643,69 +654,81 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <f>SUM(C8:H8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="1">
-        <f>SUM(I3:I7)</f>
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
-      <c r="B11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="3">
-        <v>45971</v>
-      </c>
-      <c r="E11" s="3">
-        <v>45972</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
+      <c r="C9" s="1">
+        <f>SUM(I3:I8)</f>
+        <v>31</v>
+      </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>45971</v>
+      </c>
+      <c r="E12" s="3">
+        <v>45972</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B14" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B15" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B16" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B17" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="1">
-        <f>SUM(C12:I14)</f>
+      <c r="C17" s="1">
+        <f>SUM(C13:I15)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B18" s="2" t="s">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.45">
+      <c r="B19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C18">
-        <f>35-(C8-C16)</f>
-        <v>7</v>
+      <c r="C19">
+        <f>35-(C9-C17)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47746CAB-B49B-432A-97F1-B93BE964E326}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8964D87-20CB-45B4-B8E2-3CC60017EEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
@@ -545,16 +545,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D710C5DD-EB3F-405B-9177-DB5793DB6340}">
-  <dimension ref="B2:I19"/>
+  <dimension ref="B2:K19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
@@ -576,11 +578,17 @@
       <c r="H2" s="3">
         <v>45986</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3">
+        <v>45987</v>
+      </c>
+      <c r="J2" s="3">
+        <v>45989</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,23 +605,26 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <f>SUM(C3:H3)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+      <c r="K3">
+        <f>SUM(C3:J3)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="I4">
-        <f t="shared" ref="I4:I7" si="0">SUM(C4:H4)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="K4">
+        <f t="shared" ref="K4:K8" si="0">SUM(C4:J4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -623,57 +634,57 @@
       <c r="F5">
         <v>8</v>
       </c>
-      <c r="I5">
+      <c r="K5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
-      <c r="I6">
+      <c r="K6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F7">
+      <c r="J7">
         <v>4</v>
       </c>
-      <c r="I7">
+      <c r="K7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
-      <c r="I8">
-        <f>SUM(C8:H8)</f>
+      <c r="K8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="1">
-        <f>SUM(I3:I8)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
+        <f>SUM(K3:K8)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
@@ -686,29 +697,35 @@
       <c r="E12" s="3">
         <v>45972</v>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="3">
+        <v>45989</v>
+      </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
@@ -718,8 +735,8 @@
         <v>4</v>
       </c>
       <c r="C17" s="1">
-        <f>SUM(C13:I15)</f>
-        <v>1</v>
+        <f>SUM(C13:J15)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.45">

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8964D87-20CB-45B4-B8E2-3CC60017EEA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55ED7B2-C469-4D48-8647-856AA02E51BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -545,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D710C5DD-EB3F-405B-9177-DB5793DB6340}">
-  <dimension ref="B2:K19"/>
+  <dimension ref="B2:L19"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
@@ -554,9 +554,10 @@
     <col min="6" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
@@ -584,11 +585,14 @@
       <c r="J2" s="3">
         <v>45989</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3">
+        <v>45995</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -607,24 +611,24 @@
       <c r="I3">
         <v>2</v>
       </c>
-      <c r="K3">
-        <f>SUM(C3:J3)</f>
+      <c r="L3">
+        <f>SUM(C3:K3)</f>
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
-      <c r="K4">
-        <f t="shared" ref="K4:K8" si="0">SUM(C4:J4)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="L4">
+        <f t="shared" ref="L4:L8" si="0">SUM(C4:K4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
@@ -634,36 +638,33 @@
       <c r="F5">
         <v>8</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7">
+      <c r="L7">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
@@ -671,20 +672,23 @@
         <v>1</v>
       </c>
       <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="1">
-        <f>SUM(K3:K8)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
+        <f>SUM(L3:L8)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
@@ -700,11 +704,13 @@
       <c r="F12" s="3">
         <v>45989</v>
       </c>
-      <c r="G12" s="2"/>
+      <c r="G12" s="3">
+        <v>45995</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
@@ -715,17 +721,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B15" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
@@ -745,7 +751,7 @@
       </c>
       <c r="C19">
         <f>35-(C9-C17)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55ED7B2-C469-4D48-8647-856AA02E51BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B64F74B-CC5A-4557-8813-54328BBBF55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
@@ -705,7 +705,7 @@
         <v>45989</v>
       </c>
       <c r="G12" s="3">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -720,6 +720,9 @@
       <c r="F13">
         <v>2</v>
       </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B14" s="2" t="s">
@@ -742,7 +745,7 @@
       </c>
       <c r="C17" s="1">
         <f>SUM(C13:J15)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.45">
@@ -751,7 +754,7 @@
       </c>
       <c r="C19">
         <f>35-(C9-C17)</f>
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B64F74B-CC5A-4557-8813-54328BBBF55B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC1C8FC-D5C6-453F-99D3-51AEE48A1476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>루멘스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,6 +131,18 @@
   </si>
   <si>
     <t>고장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_251215_ver10, 20, 30, 40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"25. 12. 15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Low Current Mode 작동 시 적용되는 Vref</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -765,7 +777,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
-  <dimension ref="B2:E5"/>
+  <dimension ref="B2:E6"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
@@ -828,6 +840,20 @@
         <v>20</v>
       </c>
     </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B6" s="4">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
+++ b/XD_JIG/XD04/XD04_LED_Module_Control_BD/Docs/xdic_led_module_반출내역.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD04\XD04_LED_Module_Control_BD\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC1C8FC-D5C6-453F-99D3-51AEE48A1476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CB3B6D-1036-4D81-BF42-3BE24C196DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
+    <workbookView xWindow="76575" yWindow="3375" windowWidth="21600" windowHeight="12675" activeTab="1" xr2:uid="{4213BFC1-987B-470C-A934-0A5A250397E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>루멘스</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -143,6 +143,28 @@
   </si>
   <si>
     <t>Low Current Mode 작동 시 적용되는 Vref</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"25. 12. 19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_251219.hex</t>
+  </si>
+  <si>
+    <t>Low Current Mode 사양 fix, PAM : 25mA, PWM 0.122%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>xdic_led_module_control_bd_release_260106.hex</t>
+  </si>
+  <si>
+    <t>"26. 01. 06</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주페이 방문 당시 다운로드 해줬던 버전, 12/19와 차이 없음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -777,14 +799,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB5E52BB-E1D5-4646-A95E-7F5D1E996CD9}">
-  <dimension ref="B2:E6"/>
+  <dimension ref="B2:E8"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.58203125" customWidth="1"/>
     <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
@@ -854,6 +876,34 @@
         <v>26</v>
       </c>
     </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B7" s="4">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B8" s="4">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
